--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487480_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487480_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4092</v>
+        <v>7.6186</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3428</v>
+        <v>5.6858</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0664</v>
+        <v>1.9327</v>
       </c>
       <c r="G2" t="n">
         <v>3.7928</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3765</v>
+        <v>0.5859</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7399</v>
+        <v>0.0829</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6367</v>
+        <v>0.503</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0896</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.051</v>
+        <v>7.0068</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3065</v>
+        <v>4.8346</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7445</v>
+        <v>2.1722</v>
       </c>
       <c r="G3" t="n">
         <v>3.219</v>
@@ -688,13 +688,13 @@
         <v>3.1336</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7247</v>
+        <v>0.2311</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1559</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0407</v>
+        <v>0.387</v>
       </c>
       <c r="V3" t="n">
         <v>1.4023</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ FRAIZ</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5251</v>
+        <v>2.8829</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4766</v>
+        <v>0.4201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0485</v>
+        <v>2.4628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2167</v>
+        <v>1.4859</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1419</v>
+        <v>1.6976</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3585</v>
+        <v>-0.2117</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8844</v>
+        <v>2.7515</v>
       </c>
       <c r="K4" t="n">
-        <v>1.082</v>
+        <v>2.3069</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8024</v>
+        <v>0.4446</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6677</v>
+        <v>-1.2656</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2239</v>
+        <v>-0.6093</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>-0.6563</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1751</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7149</v>
+        <v>-0.0237</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1227</v>
+        <v>0.491</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5816</v>
+        <v>2.7917</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5816</v>
+        <v>0.6914</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>J. DOMINGUEZ FRAIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6105</v>
+        <v>2.724</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2533</v>
+        <v>2.8626</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8638</v>
+        <v>-0.1386</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4859</v>
+        <v>2.2167</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6976</v>
+        <v>-0.1419</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2117</v>
+        <v>2.3585</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7515</v>
+        <v>2.8844</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3069</v>
+        <v>1.082</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4446</v>
+        <v>1.8024</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2656</v>
+        <v>-0.6677</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6093</v>
+        <v>-1.2239</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6563</v>
+        <v>0.5562</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2961</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.188</v>
+        <v>-0.0218</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8919</v>
+        <v>0.9356</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7917</v>
+        <v>-1.5816</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6914</v>
+        <v>-1.5816</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0401</v>
+        <v>1.7553</v>
       </c>
       <c r="E6" t="n">
-        <v>2.728</v>
+        <v>3.2562</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.688</v>
+        <v>-1.5009</v>
       </c>
       <c r="G6" t="n">
         <v>2.7376</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4869</v>
+        <v>0.2283</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>0.0529</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0117</v>
+        <v>0.1754</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1899</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2907</v>
+        <v>0.3174</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2907</v>
+        <v>0.3174</v>
       </c>
       <c r="G7" t="n">
         <v>0.2729</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3332</v>
+        <v>-0.2158</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5574</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2242</v>
+        <v>0.3846</v>
       </c>
       <c r="G8" t="n">
         <v>0.2718</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.113</v>
+        <v>0.0044</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0288</v>
+        <v>-0.0141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1419</v>
+        <v>0.0185</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8837</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.461</v>
+        <v>-0.4108</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0751</v>
+        <v>-0.8111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6141</v>
+        <v>0.4003</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0121</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3921</v>
+        <v>0.4423</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.5346</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0576</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0331</v>
+        <v>-0.9796</v>
       </c>
       <c r="E10" t="n">
         <v>-0.801</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2321</v>
+        <v>-0.1786</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8135</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2196</v>
+        <v>-0.1661</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>J. CONNELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.164</v>
+        <v>-2.3849</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1454</v>
+        <v>-5.997</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0187</v>
+        <v>3.6121</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0678</v>
+        <v>-3.2325</v>
       </c>
       <c r="H11" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.558</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0764</v>
+        <v>-4.7905</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2543</v>
+        <v>-3.2522</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3471</v>
+        <v>1.9632</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>-5.2154</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8135</v>
+        <v>0.0197</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3385</v>
+        <v>-0.4052</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.475</v>
+        <v>0.4249</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>2.9377</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1008</v>
+        <v>1.1229</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0882</v>
+        <v>0.1929</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0126</v>
+        <v>0.93</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3905</v>
+        <v>-0.2754</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3905</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CONNELL</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3747</v>
+        <v>-2.6268</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0135</v>
+        <v>-1.5547</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6388</v>
+        <v>-1.0721</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2325</v>
+        <v>-2.0678</v>
       </c>
       <c r="H12" t="n">
-        <v>1.558</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.7905</v>
+        <v>-2.0764</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2522</v>
+        <v>-0.2543</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9632</v>
+        <v>0.3471</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.2154</v>
+        <v>-0.6014</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0197</v>
+        <v>-1.8135</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4052</v>
+        <v>-0.3385</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4249</v>
+        <v>-1.475</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9377</v>
+        <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1332</v>
+        <v>-0.362</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1764</v>
+        <v>-0.3211</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9567</v>
+        <v>-0.0409</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2754</v>
+        <v>0.3905</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2754</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2187</v>
+        <v>-5.7513</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8246</v>
+        <v>-5.5176</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3941</v>
+        <v>-0.2337</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2041</v>
@@ -1468,13 +1468,13 @@
         <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.76</v>
+        <v>-0.2926</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.891</v>
+        <v>-0.584</v>
       </c>
       <c r="U13" t="n">
-        <v>0.131</v>
+        <v>0.2914</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8837</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.341899999999997</v>
+        <v>9.935799999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>1.183599999999999</v>
+        <v>1.7776</v>
       </c>
       <c r="F14" t="n">
-        <v>8.158099999999999</v>
+        <v>8.158199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>4.666700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.405900000000001</v>
+        <v>3.4059</v>
       </c>
       <c r="I14" t="n">
         <v>1.2605</v>
@@ -1522,7 +1522,7 @@
         <v>12.95339999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>7.124600000000001</v>
+        <v>7.1246</v>
       </c>
       <c r="L14" t="n">
         <v>5.828799999999999</v>
@@ -1534,7 +1534,7 @@
         <v>-3.7186</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.568099999999999</v>
+        <v>-4.5681</v>
       </c>
       <c r="P14" t="n">
         <v>3.917000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>17.6262</v>
       </c>
       <c r="S14" t="n">
-        <v>2.135000000000001</v>
+        <v>2.728899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0879</v>
+        <v>-1.4939</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2228</v>
+        <v>4.2229</v>
       </c>
       <c r="V14" t="n">
         <v>-1.377</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3161</v>
+        <v>5.0358</v>
       </c>
       <c r="E15" t="n">
-        <v>6.212</v>
+        <v>5.905</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8959</v>
+        <v>-0.8692</v>
       </c>
       <c r="G15" t="n">
         <v>1.6834</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.101</v>
+        <v>-0.3813</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3276</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2266</v>
+        <v>0.2533</v>
       </c>
       <c r="V15" t="n">
         <v>2.1669</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6436</v>
+        <v>1.7413</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6385</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0051</v>
+        <v>0.8982</v>
       </c>
       <c r="G16" t="n">
         <v>1.9788</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6106</v>
+        <v>-0.5129</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7546</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.144</v>
+        <v>0.0371</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1196</v>
+        <v>0.7519</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4292</v>
+        <v>-0.2245</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5487</v>
+        <v>0.9764</v>
       </c>
       <c r="G17" t="n">
         <v>2.511</v>
@@ -1780,13 +1780,13 @@
         <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5963</v>
+        <v>-0.964</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1704</v>
+        <v>-0.9657</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4259</v>
+        <v>0.0018</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5993000000000001</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3172</v>
+        <v>-0.3707</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5838</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2666</v>
+        <v>0.2131</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5962</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.279</v>
+        <v>0.2256</v>
       </c>
       <c r="T18" t="n">
         <v>0.0176</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2614</v>
+        <v>0.2079</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3365</v>
+        <v>-0.6481</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7713</v>
+        <v>-0.976</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4348</v>
+        <v>0.3279</v>
       </c>
       <c r="G19" t="n">
         <v>0.6147</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0295</v>
+        <v>-0.3411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.09</v>
+        <v>-0.2947</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0605</v>
+        <v>-0.0465</v>
       </c>
       <c r="V19" t="n">
         <v>0.0576</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5661</v>
+        <v>-2.6639</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.091</v>
+        <v>-1.2957</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4751</v>
+        <v>-1.3682</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3862</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3618</v>
+        <v>0.2641</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0465</v>
+        <v>-0.1582</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3154</v>
+        <v>0.4223</v>
       </c>
       <c r="V20" t="n">
         <v>-1.15</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.982</v>
+        <v>-2.7552</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2528</v>
+        <v>-1.9458</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7292</v>
+        <v>-0.8094</v>
       </c>
       <c r="G21" t="n">
         <v>-5.1659</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0535</v>
+        <v>0.1734</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3564</v>
+        <v>-0.0494</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3029</v>
+        <v>0.2228</v>
       </c>
       <c r="V21" t="n">
         <v>2.4332</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2135</v>
+        <v>-3.3457</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9652</v>
+        <v>-2.5197</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2483</v>
+        <v>-0.826</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8257</v>
+        <v>-1.8679</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0178</v>
+        <v>-0.2364</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1921</v>
+        <v>-1.6314</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7038</v>
+        <v>0.5311</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0668</v>
+        <v>0.4406</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.637</v>
+        <v>0.0905</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1219</v>
+        <v>-2.3989</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.951</v>
+        <v>-0.677</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8290999999999999</v>
+        <v>-1.7219</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1751</v>
+        <v>-4.1128</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1751</v>
+        <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5523</v>
+        <v>-0.1942</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0288</v>
+        <v>-0.4299</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5234</v>
+        <v>0.2357</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9401</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1152</v>
+        <v>1.492</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8249</v>
+        <v>-0.8171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2701</v>
+        <v>-3.4018</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4174</v>
+        <v>-3.9157</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8527</v>
+        <v>0.5138</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8679</v>
+        <v>-0.6127</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2364</v>
+        <v>-1.5226</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6314</v>
+        <v>0.9099</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5311</v>
+        <v>1.5123</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4406</v>
+        <v>-0.4373</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0905</v>
+        <v>1.9496</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3989</v>
+        <v>-2.125</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.677</v>
+        <v>-1.0853</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7219</v>
+        <v>-1.0397</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9585</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q23" t="n">
         <v>-4.1128</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1186</v>
+        <v>-0.4848</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3276</v>
+        <v>-0.9822</v>
       </c>
       <c r="U23" t="n">
-        <v>0.209</v>
+        <v>0.4974</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6749000000000001</v>
+        <v>-0.5417</v>
       </c>
       <c r="W23" t="n">
-        <v>1.492</v>
+        <v>-0.3329</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8171</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7356</v>
+        <v>-3.6855</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2227</v>
+        <v>-3.1699</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4871</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6127</v>
+        <v>-1.8257</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5226</v>
+        <v>-2.0178</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9099</v>
+        <v>0.1921</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5123</v>
+        <v>-1.7038</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4373</v>
+        <v>-1.0668</v>
       </c>
       <c r="L24" t="n">
-        <v>1.9496</v>
+        <v>-0.637</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.125</v>
+        <v>-0.1219</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0853</v>
+        <v>-0.951</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0397</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.1128</v>
+        <v>-1.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8185</v>
+        <v>0.0803</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2892</v>
+        <v>-0.1759</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4707</v>
+        <v>0.2561</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5417</v>
+        <v>-1.9401</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3329</v>
+        <v>-0.1152</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2088</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.341699999999999</v>
+        <v>-9.341899999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-7.882899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4589</v>
+        <v>-1.459</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6667</v>
@@ -2410,7 +2410,7 @@
         <v>-4.2229</v>
       </c>
       <c r="U25" t="n">
-        <v>2.088</v>
+        <v>2.0879</v>
       </c>
       <c r="V25" t="n">
         <v>1.3769</v>
